--- a/English/TOEFL/刷题/刷题.xlsx
+++ b/English/TOEFL/刷题/刷题.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Blog\English\TOEFL\刷题\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229B30BA-F551-435A-AE71-736FBC5A873A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7367C49-C596-4C73-B85C-E78172265172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4185" yWindow="2010" windowWidth="20910" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14865" yWindow="0" windowWidth="13935" windowHeight="16200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="听力" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
   <si>
     <t>4/5</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -66,6 +66,18 @@
   </si>
   <si>
     <t>5/5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9/10</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -588,7 +600,9 @@
       <c r="G11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="2"/>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="2">
@@ -600,6 +614,9 @@
       <c r="D12" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E12" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>10</v>
       </c>
@@ -616,18 +633,26 @@
       <c r="D13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="G13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="2">
         <v>42</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -1254,9 +1279,12 @@
         <v>44</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="C12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -1290,7 +1318,9 @@
         <v>41</v>
       </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="C15" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -1781,6 +1811,9 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" display="TPO" xr:uid="{6C84BCAF-4EAC-4740-AAB4-867B2583C163}"/>
+    <hyperlink ref="C12" r:id="rId2" xr:uid="{F9A357E3-6355-4B99-BD9F-CE36BAA4F568}"/>
+    <hyperlink ref="E12" r:id="rId3" xr:uid="{EA2940A2-80DB-4A17-810C-06498F70F8CF}"/>
+    <hyperlink ref="C15" r:id="rId4" xr:uid="{1AE850C8-3D3A-41F2-882E-533B83D733F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/English/TOEFL/刷题/刷题.xlsx
+++ b/English/TOEFL/刷题/刷题.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Blog\English\TOEFL\刷题\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7367C49-C596-4C73-B85C-E78172265172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5F9D1D-FD04-4AE1-9E3C-EFCDB68A7DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14865" yWindow="0" windowWidth="13935" windowHeight="16200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11850" yWindow="2340" windowWidth="15465" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="听力" sheetId="1" r:id="rId1"/>
@@ -98,12 +98,14 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -847,8 +849,11 @@
       <c r="H31" s="2"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A32" s="2">
+      <c r="A32" s="5">
         <v>24</v>
+      </c>
+      <c r="B32" s="3">
+        <v>27</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -1115,9 +1120,10 @@
   <hyperlinks>
     <hyperlink ref="A11" r:id="rId1" display="https://toefl.kmf.com/exam/resultsum/170390377482489233" xr:uid="{359E21E2-2C9F-4833-B35E-A610633A024A}"/>
     <hyperlink ref="A1" r:id="rId2" xr:uid="{094C876D-3158-412E-B0BD-0BF9E0F8DECE}"/>
+    <hyperlink ref="A32" r:id="rId3" display="https://toefl.kmf.com/exam/resultsum/170481232106856180/1" xr:uid="{6F4CA4B5-3364-4171-9D92-FF92C8A551E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
